--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises. Maman dit : on va compter des objets. Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Noé dit : dix fraises. Maman sourit. Il dit le nombre. Dix. Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre. Maman dit : tu as compté des objets. Noé sent une fraise. Elle sent le sucre.</t>
+          <t>Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises. On va compter des objets. Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Dix fraises. Maman sourit. Il dit le nombre. Dix. Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre. Tu as compté des objets. Noé sent une fraise. Elle sent le sucre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises.
+maman|On va compter des objets.
+narrateur|Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix.
+enfant-m|Dix fraises. Maman sourit. Il dit le nombre. Dix.
+narrateur|Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre.
+maman|Tu as compté des objets.
+narrateur|Noé sent une fraise. Elle sent le sucre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé compte les fraises. Combien y en a-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le bol. Noé garde une fraise. Il croque.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Noé sent une fraise. Elle sent le sucre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Noé compte les fraises. Combien y en a-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Noé a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1841,7 @@
           <t>narrateur|Maman range le bol. Noé garde une fraise. Il croque.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé compte jusqu'à dix</t>
+          <t>Nino compte les fraises</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte tombe du robinet. Nino touche les fraises du bol rouge. Il compte jusqu'à dix. Papa et maman disent le nombre avec lui.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises. On va compter des objets. Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Dix fraises. Maman sourit. Il dit le nombre. Dix. Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre. Tu as compté des objets. Noé sent une fraise. Elle sent le sucre.</t>
+          <t>Le robinet laisse une goutte. La goutte tape l'évier. Ça fait un petit ping. Le carrelage est frais sous les pieds. Un torchon à carreaux pend. Les carreaux sont blancs et rouges. La fenêtre est un peu embuée. Ça sent le sucre des fraises. Un bol rouge attend sur la table. Le bol est lisse et froid. Nino, tu entends la goutte ? Oui, maman. Ça tape. Le bol est prêt. Ça sent bon, ici. En ce moment, Nino s'approche du bol. Dedans, des fraises. Elles sont petites et brillantes. On compte des objets. On touche. On dit le nombre. Nino touche une fraise. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. Tu dis le nombre. Papa en pose encore. Les fraises roulent un peu. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as compté des objets. Dix. Bravo, Nino. Tu as fait du bon travail. Nino pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Jusqu'à dix. Une goutte tombe encore. Le torchon reste calme. On essuie le bord du bol ? Oui, maman. Nino passe le torchon tout doux. Le bol redevient mat. Ça sent encore le sucre. C'est sucré. Maman sort un petit bol bleu. Dedans, des framboises. Elles sont molles et sombres. On compte aussi celles-là. Nino touche une framboise. Une. Deux. Trois. Quatre. Cinq. Cinq framboises. Tu dis le nombre. Cinq. Tu as compté des objets. Le bol bleu est froid aussi. Une goutte sèche sur l'évier. Les deux bols sont prêts. Rouge et bleu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises.
-maman|On va compter des objets.
-narrateur|Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix.
-enfant-m|Dix fraises. Maman sourit. Il dit le nombre. Dix.
-narrateur|Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre.
+          <t>narrateur|Le robinet laisse une goutte.
+narrateur|La goutte tape l'évier.
+narrateur|Ça fait un petit ping.
+narrateur|Le carrelage est frais sous les pieds.
+narrateur|Un torchon à carreaux pend.
+narrateur|Les carreaux sont blancs et rouges.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Ça sent le sucre des fraises.
+narrateur|Un bol rouge attend sur la table.
+narrateur|Le bol est lisse et froid.
+maman|Nino, tu entends la goutte ?
+enfant-m|Oui, maman.
+enfant-m|Ça tape.
+papa|Le bol est prêt.
+maman|Ça sent bon, ici.
+narrateur|En ce moment, Nino s'approche du bol.
+narrateur|Dedans, des fraises.
+narrateur|Elles sont petites et brillantes.
+papa|On compte des objets.
+maman|On touche. On dit le nombre.
+narrateur|Nino touche une fraise.
+enfant-m|Une.
+narrateur|Il en touche une autre.
+enfant-m|Deux.
+enfant-m|Trois.
+enfant-m|Quatre.
+enfant-m|Cinq.
+papa|Cinq fraises.
+maman|Tu dis le nombre.
+narrateur|Papa en pose encore.
+narrateur|Les fraises roulent un peu.
+enfant-m|Six.
+enfant-m|Sept.
+enfant-m|Huit.
+enfant-m|Neuf.
+enfant-m|Dix.
+papa|Dix fraises.
 maman|Tu as compté des objets.
-narrateur|Noé sent une fraise. Elle sent le sucre.</t>
+enfant-m|Dix.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino pose les fraises une à une.
+narrateur|Une, deux, trois, quatre, cinq.
+narrateur|Six, sept, huit, neuf, dix.
+maman|Les objets sont là.
+papa|Jusqu'à dix.
+narrateur|Une goutte tombe encore.
+narrateur|Le torchon reste calme.
+maman|On essuie le bord du bol ?
+enfant-m|Oui, maman.
+narrateur|Nino passe le torchon tout doux.
+narrateur|Le bol redevient mat.
+papa|Ça sent encore le sucre.
+enfant-m|C'est sucré.
+narrateur|Maman sort un petit bol bleu.
+narrateur|Dedans, des framboises.
+narrateur|Elles sont molles et sombres.
+maman|On compte aussi celles-là.
+narrateur|Nino touche une framboise.
+enfant-m|Une. Deux. Trois. Quatre. Cinq.
+papa|Cinq framboises.
+maman|Tu dis le nombre.
+enfant-m|Cinq.
+papa|Tu as compté des objets.
+narrateur|Le bol bleu est froid aussi.
+narrateur|Une goutte sèche sur l'évier.
+maman|Les deux bols sont prêts.
+enfant-m|Rouge et bleu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé compte les fraises. Combien y en a-t-il ?</t>
+          <t>Nino compte les fraises. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1579,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé compte les fraises. Combien y en a-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino compte les fraises.
+narrateur|Combien y en a-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix.</t>
+          <t>Nino a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Tu as dit dix ? Oui, maman. Bravo, Nino. Tu as fait du bon travail. Le bol rouge reste sur la table. Il est un peu froid. Les fraises sont à leur place ? Oui, maman. Une fraise brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1747,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a compté des objets.
+narrateur|Dix fraises.
+narrateur|Il a dit le nombre.
+narrateur|Jusqu'à dix.
+maman|Tu as dit dix ?
+enfant-m|Oui, maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Le bol rouge reste sur la table.
+narrateur|Il est un peu froid.
+maman|Les fraises sont à leur place ?
+enfant-m|Oui, maman.
+narrateur|Une fraise brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le bol. Noé garde une fraise. Il croque.</t>
+          <t>Nino pose le torchon. Je te verse un peu d'eau ? Oui, maman. Maman ferme le robinet. La goutte s'arrête. Tu as fini de compter ? Oui, papa. Bravo. Le bol sent encore le sucre. On goûte une fraise ? Oui. C'est doux, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1922,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le bol. Noé garde une fraise. Il croque.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino pose le torchon.
+maman|Je te verse un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Maman ferme le robinet.
+narrateur|La goutte s'arrête.
+papa|Tu as fini de compter ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le bol sent encore le sucre.
+maman|On goûte une fraise ?
+enfant-m|Oui.
+narrateur|C'est doux, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino tient le bol des deux mains. Les fraises sentent le sucre. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,10 +2100,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nino tient le bol des deux mains.
+narrateur|Les fraises sentent le sucre.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-m|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino compte les fraises</t>
+          <t>Le bol rouge d'Amir</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une goutte tombe du robinet. Nino touche les fraises du bol rouge. Il compte jusqu'à dix. Papa et maman disent le nombre avec lui.</t>
+          <t>La confiture fait des bulles. Amir touche les fraises du bol rouge. Une à dix. Il dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le robinet laisse une goutte. La goutte tape l'évier. Ça fait un petit ping. Le carrelage est frais sous les pieds. Un torchon à carreaux pend. Les carreaux sont blancs et rouges. La fenêtre est un peu embuée. Ça sent le sucre des fraises. Un bol rouge attend sur la table. Le bol est lisse et froid. Nino, tu entends la goutte ? Oui, maman. Ça tape. Le bol est prêt. Ça sent bon, ici. En ce moment, Nino s'approche du bol. Dedans, des fraises. Elles sont petites et brillantes. On compte des objets. On touche. On dit le nombre. Nino touche une fraise. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. Tu dis le nombre. Papa en pose encore. Les fraises roulent un peu. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as compté des objets. Dix. Bravo, Nino. Tu as fait du bon travail. Nino pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Jusqu'à dix. Une goutte tombe encore. Le torchon reste calme. On essuie le bord du bol ? Oui, maman. Nino passe le torchon tout doux. Le bol redevient mat. Ça sent encore le sucre. C'est sucré. Maman sort un petit bol bleu. Dedans, des framboises. Elles sont molles et sombres. On compte aussi celles-là. Nino touche une framboise. Une. Deux. Trois. Quatre. Cinq. Cinq framboises. Tu dis le nombre. Cinq. Tu as compté des objets. Le bol bleu est froid aussi. Une goutte sèche sur l'évier. Les deux bols sont prêts. Rouge et bleu.</t>
+          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. C'est du bon travail. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé et maman sont dans la cuisine. Il y a un bol. Dedans, des fraises. Maman dit : on va &lt;emphasis level="moderate"&gt;compter&lt;/emphasis&gt; des objets. Noé touche une fraise. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Noé dit : dix fraises. Maman sourit. Il dit le nombre. Dix. Noé pose les fraises. Une, deux, trois, quatre, cinq, six, sept, huit, neuf, dix. Les objets sont là. Noé les compte jusqu'à dix. Le bol est rouge. Parce qu'il compte, il dit le nombre. Maman dit : tu as compté des objets. Noé sent une fraise. Elle sent le sucre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. C'est du bon travail. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,74 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le robinet laisse une goutte.
-narrateur|La goutte tape l'évier.
-narrateur|Ça fait un petit ping.
-narrateur|Le carrelage est frais sous les pieds.
-narrateur|Un torchon à carreaux pend.
-narrateur|Les carreaux sont blancs et rouges.
-narrateur|La fenêtre est un peu embuée.
-narrateur|Ça sent le sucre des fraises.
+          <t>narrateur|La casserole de confiture fait des bulles douces.
+narrateur|Ça sent le sucre chaud.
 narrateur|Un bol rouge attend sur la table.
-narrateur|Le bol est lisse et froid.
-maman|Nino, tu entends la goutte ?
+narrateur|Des grains de sucre brillent sur le bois.
+narrateur|Le torchon est encore un peu humide.
+narrateur|La fenêtre est entrouverte.
+narrateur|Un oiseau chante, tout près.
+maman|Tu as senti, Amir ?
 enfant-m|Oui, maman.
-enfant-m|Ça tape.
-papa|Le bol est prêt.
-maman|Ça sent bon, ici.
-narrateur|En ce moment, Nino s'approche du bol.
+enfant-m|Ça sent le sucre.
+maman|C'est la confiture.
+narrateur|En ce moment, Amir s'approche de la table.
+narrateur|Le bol rouge est plein.
 narrateur|Dedans, des fraises.
 narrateur|Elles sont petites et brillantes.
-papa|On compte des objets.
-maman|On touche. On dit le nombre.
-narrateur|Nino touche une fraise.
+maman|On va compter des objets.
+maman|Des fraises.
+enfant-m|Des fraises.
+narrateur|Amir touche une fraise.
+narrateur|Elle est froide et un peu sucrée.
+maman|Une.
 enfant-m|Une.
 narrateur|Il en touche une autre.
 enfant-m|Deux.
 enfant-m|Trois.
 enfant-m|Quatre.
 enfant-m|Cinq.
-papa|Cinq fraises.
-maman|Tu dis le nombre.
-narrateur|Papa en pose encore.
-narrateur|Les fraises roulent un peu.
+maman|Cinq fraises.
+maman|On continue.
 enfant-m|Six.
 enfant-m|Sept.
 enfant-m|Huit.
 enfant-m|Neuf.
 enfant-m|Dix.
-papa|Dix fraises.
+enfant-m|Dix fraises.
+maman|Tu as dit le nombre.
+maman|Dix.
+maman|Bravo, Amir.
 maman|Tu as compté des objets.
+maman|C'est du bon travail.
+narrateur|Le bol est rouge et lisse.
+maman|On pose les fraises ?
+enfant-m|Oui, maman.
+narrateur|Amir pose les fraises une à une.
+enfant-m|Une, deux, trois, quatre, cinq.
+enfant-m|Six, sept, huit, neuf, dix.
+maman|Les objets sont là.
+maman|Tu les as comptés jusqu'à dix.
 enfant-m|Dix.
-papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
-narrateur|Nino pose les fraises une à une.
-narrateur|Une, deux, trois, quatre, cinq.
-narrateur|Six, sept, huit, neuf, dix.
-maman|Les objets sont là.
-papa|Jusqu'à dix.
-narrateur|Une goutte tombe encore.
-narrateur|Le torchon reste calme.
-maman|On essuie le bord du bol ?
+maman|Oui.
+maman|Tu as dit le nombre.
+narrateur|Amir sent une fraise.
+enfant-m|Elle sent le sucre.
+maman|Oui.
+maman|Un peu le jardin aussi.
+narrateur|La casserole chante encore, tout doux.
+narrateur|Une bulle éclate, tout petit.
+maman|Tu as fini de compter ?
 enfant-m|Oui, maman.
-narrateur|Nino passe le torchon tout doux.
-narrateur|Le bol redevient mat.
-papa|Ça sent encore le sucre.
-enfant-m|C'est sucré.
-narrateur|Maman sort un petit bol bleu.
-narrateur|Dedans, des framboises.
-narrateur|Elles sont molles et sombres.
-maman|On compte aussi celles-là.
-narrateur|Nino touche une framboise.
-enfant-m|Une. Deux. Trois. Quatre. Cinq.
-papa|Cinq framboises.
-maman|Tu dis le nombre.
-enfant-m|Cinq.
-papa|Tu as compté des objets.
-narrateur|Le bol bleu est froid aussi.
-narrateur|Une goutte sèche sur l'évier.
-maman|Les deux bols sont prêts.
-enfant-m|Rouge et bleu.</t>
+enfant-m|Dix.
+maman|Bravo.
+maman|Tu as compté des objets.
+narrateur|Le torchon sent encore le savon.
+narrateur|L'oiseau chante encore, tout près.
+maman|Tu veux essuyer la table ?
+enfant-m|Oui.
+narrateur|Amir passe le torchon.
+narrateur|Le bois redevient lisse.
+maman|Bravo.
+maman|Tu as compté des objets.
+enfant-m|Dix fraises dans le bol.
+maman|Oui.
+maman|Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1423,12 +1428,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nino compte les fraises. Combien y en a-t-il ?</t>
+          <t>Amir compte les fraises. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé compte les fraises. Combien y en a-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir compte les fraises. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1584,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nino compte les fraises.
+          <t>narrateur|Amir compte les fraises.
 narrateur|Combien y en a-t-il ?</t>
         </is>
       </c>
@@ -1607,12 +1612,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Tu as dit dix ? Oui, maman. Bravo, Nino. Tu as fait du bon travail. Le bol rouge reste sur la table. Il est un peu froid. Les fraises sont à leur place ? Oui, maman. Une fraise brille encore.</t>
+          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Tu as fait du bon travail. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Tu as fait du bon travail. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,19 +1752,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a compté des objets.
+          <t>narrateur|Amir a compté des objets.
 narrateur|Dix fraises.
 narrateur|Il a dit le nombre.
 narrateur|Jusqu'à dix.
-maman|Tu as dit dix ?
-enfant-m|Oui, maman.
-papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
-narrateur|Le bol rouge reste sur la table.
-narrateur|Il est un peu froid.
-maman|Les fraises sont à leur place ?
-enfant-m|Oui, maman.
-narrateur|Une fraise brille encore.</t>
+maman|Dix.
+maman|Bravo, Amir.
+enfant-m|Dix fraises.
+maman|Tu as fait du bon travail.
+narrateur|Le bol rouge reste au milieu.
+narrateur|Ça sent encore le sucre chaud.</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1788,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose le torchon. Je te verse un peu d'eau ? Oui, maman. Maman ferme le robinet. La goutte s'arrête. Tu as fini de compter ? Oui, papa. Bravo. Le bol sent encore le sucre. On goûte une fraise ? Oui. C'est doux, tout près.</t>
+          <t>On range le bol ? Oui, maman. Maman range le bol. Amir garde une fraise. Tu croques ? Oui. Il croque. C'est sucré. Tu as fini ta fraise ? Oui, maman. Bravo. Les grains de sucre brillent encore. On laisse la confiture finir ? Oui, maman. Ils restent un moment. La casserole fait encore des bulles. Tu as bien compté. Jusqu'à dix. Le bol rouge brille encore. L'oiseau se tait un moment.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le bol. Noé garde une fraise. Il croque.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le bol ? Oui, maman. Maman range le bol. Amir garde une fraise. Tu croques ? Oui. Il croque. C'est sucré. Tu as fini ta fraise ? Oui, maman. Bravo. Les grains de sucre brillent encore. On laisse la confiture finir ? Oui, maman. Ils restent un moment. La casserole fait encore des bulles. Tu as bien compté. Jusqu'à dix. Le bol rouge brille encore. L'oiseau se tait un moment.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,18 +1924,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino pose le torchon.
-maman|Je te verse un peu d'eau ?
+          <t>maman|On range le bol ?
 enfant-m|Oui, maman.
-narrateur|Maman ferme le robinet.
-narrateur|La goutte s'arrête.
-papa|Tu as fini de compter ?
-enfant-m|Oui, papa.
-papa|Bravo.
-narrateur|Le bol sent encore le sucre.
-maman|On goûte une fraise ?
+narrateur|Maman range le bol.
+narrateur|Amir garde une fraise.
+maman|Tu croques ?
 enfant-m|Oui.
-narrateur|C'est doux, tout près.</t>
+narrateur|Il croque.
+narrateur|C'est sucré.
+maman|Tu as fini ta fraise ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Les grains de sucre brillent encore.
+maman|On laisse la confiture finir ?
+enfant-m|Oui, maman.
+narrateur|Ils restent un moment.
+narrateur|La casserole fait encore des bulles.
+maman|Tu as bien compté.
+enfant-m|Jusqu'à dix.
+narrateur|Le bol rouge brille encore.
+narrateur|L'oiseau se tait un moment.</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino tient le bol des deux mains. Les fraises sentent le sucre. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2110,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Nino tient le bol des deux mains.
-narrateur|Les fraises sentent le sucre.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-m|Oui.
+          <t>enfant-m|Dix fraises.
+maman|Tu as compté des objets.
+maman|Jusqu'à dix.
+maman|Bravo, Amir.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2126,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2180,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. C'est du bon travail. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
+          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. C'est du bon travail. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
+          <t>La casserole de confiture fait des bulles douces. Ça sent le sucre chaud. Un bol rouge attend sur la table. Des grains de sucre brillent sur le bois. Le torchon est encore un peu humide. La fenêtre est entrouverte. Un oiseau chante, tout près. Tu as senti, Amir ? Oui, maman. Ça sent le sucre. C'est la confiture. En ce moment, Amir s'approche de la table. Le bol rouge est plein. Dedans, des fraises. Elles sont petites et brillantes. On va compter des objets. Des fraises. Des fraises. Amir touche une fraise. Elle est froide et un peu sucrée. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq fraises. On continue. Six. Sept. Huit. Neuf. Dix. Dix fraises. Tu as dit le nombre. Dix. Bravo, Amir. Tu as compté des objets. Le bol est rouge et lisse. On pose les fraises ? Oui, maman. Amir pose les fraises une à une. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés jusqu'à dix. Dix. Oui. Tu as dit le nombre. Amir sent une fraise. Elle sent le sucre. Oui. Un peu le jardin aussi. La casserole chante encore, tout doux. Une bulle éclate, tout petit. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le torchon sent encore le savon. L'oiseau chante encore, tout près. Tu veux essuyer la table ? Oui. Amir passe le torchon. Le bois redevient lisse. Bravo. Tu as compté des objets. Dix fraises dans le bol. Oui. Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 maman|Dix.
 maman|Bravo, Amir.
 maman|Tu as compté des objets.
-maman|C'est du bon travail.
 narrateur|Le bol est rouge et lisse.
 maman|On pose les fraises ?
 enfant-m|Oui, maman.
@@ -1612,12 +1611,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Tu as fait du bon travail. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
+          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Tu as fait du bon travail. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
+          <t>Amir a compté des objets. Dix fraises. Il a dit le nombre. Jusqu'à dix. Dix. Bravo, Amir. Dix fraises. Le bol rouge reste au milieu. Ça sent encore le sucre chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1758,6 @@
 maman|Dix.
 maman|Bravo, Amir.
 enfant-m|Dix fraises.
-maman|Tu as fait du bon travail.
 narrateur|Le bol rouge reste au milieu.
 narrateur|Ça sent encore le sucre chaud.</t>
         </is>
@@ -1970,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir. L'histoire est finie.</t>
+          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir. L'histoire est finie.</t>
+          <t>Dix fraises. Tu as compté des objets. Jusqu'à dix. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,8 +2111,7 @@
           <t>enfant-m|Dix fraises.
 maman|Tu as compté des objets.
 maman|Jusqu'à dix.
-maman|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Amir.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2182,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
